--- a/analises/vinhos/tanyno-champagnes-agosto-2026.xlsx
+++ b/analises/vinhos/tanyno-champagnes-agosto-2026.xlsx
@@ -418,56 +418,44 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Linha</t>
+          <t>Produtor</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Produtor</t>
+          <t>Vinho</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Vinho</t>
+          <t>Safra</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Safra</t>
+          <t>Preço site</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Estoque</t>
+          <t>Custo c/ 5% desc.</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Preço A37</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Custo c/ 5% desc.</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Venda (markup 1,55x)</t>
         </is>
@@ -476,229 +464,79 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tanyno Autoral</t>
+          <t>Champagne Vauversin</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CHAMPAGNE VILMART</t>
+          <t>AUBELINE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CUVÉE RUBIS ROSE</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
           <t>N.V.</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>4</v>
+      <c r="D2" s="2" t="n">
+        <v>345.45</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>328.18</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>540.8</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>513.76</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>796.33</v>
+        <v>508.68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tanyno Autoral</t>
+          <t>Champagne Vauversin</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LA PARCELLE</t>
+          <t>ORIGINAL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LA CAPELLA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>9</v>
+          <t>N.V.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>345.45</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>328.18</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>915.45</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>869.6799999999999</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>1348</v>
+        <v>508.68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tanyno Autoral</t>
+          <t>Champagne Vauversin</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MARC HEBRART</t>
+          <t>ROSSIGNOL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MES FAVORITES VIEILLES VIGNES PREMIER CRU</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>N.V.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>545.0599999999999</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>517.8099999999999</v>
+      </c>
       <c r="F4" s="2" t="n">
-        <v>393.57</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>373.89</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>579.53</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Tanyno Autoral</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>MARC HEBRART</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>NOCES DE CRAIE GRAND CRU</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" s="2" t="n">
-        <v>583.22</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>554.0599999999999</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>858.79</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Tanyno Autoral</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>MARC HEBRART</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ROSÉ PREMIER CRU</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>N.V.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" s="2" t="n">
-        <v>346.11</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>328.8</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>509.64</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Tanyno Autoral</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>MARC HEBRART</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>SÉLECTION PREMIER CRU</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>N.V.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" s="2" t="n">
-        <v>295.56</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>280.78</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>435.21</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Tanyno Autoral</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ROGER COULON</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>VRIGNY ROUGE</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" s="2" t="n">
-        <v>785.27</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>746.01</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>1156.32</v>
+        <v>802.61</v>
       </c>
     </row>
   </sheetData>

--- a/analises/vinhos/tanyno-champagnes-agosto-2026.xlsx
+++ b/analises/vinhos/tanyno-champagnes-agosto-2026.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -469,7 +469,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AUBELINE</t>
+          <t>ORIGINAL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -485,58 +485,6 @@
       </c>
       <c r="F2" s="2" t="n">
         <v>508.68</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Champagne Vauversin</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ORIGINAL</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>N.V.</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>345.45</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>328.18</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>508.68</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Champagne Vauversin</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ROSSIGNOL</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>545.0599999999999</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>517.8099999999999</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>802.61</v>
       </c>
     </row>
   </sheetData>

--- a/analises/vinhos/tanyno-champagnes-agosto-2026.xlsx
+++ b/analises/vinhos/tanyno-champagnes-agosto-2026.xlsx
@@ -418,15 +418,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -447,15 +448,20 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Preço site</t>
+          <t>Preço base</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Custo c/ 5% desc.</t>
+          <t>Ajuste</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Custo final</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Venda (markup 1,55x)</t>
         </is>
@@ -480,11 +486,62 @@
       <c r="D2" s="2" t="n">
         <v>345.45</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>-5% (à vista)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
         <v>328.18</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="G2" s="2" t="n">
         <v>508.68</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Moët &amp; Chandon</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" s="2" t="n">
+        <v>375</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>+13%</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>423.75</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>656.8099999999999</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Veuve Clicquot</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" s="2" t="n">
+        <v>388</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>+13%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>438.44</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>679.58</v>
       </c>
     </row>
   </sheetData>
